--- a/it_request_forms/013_membership_support_form--it_request_forms.xlsx
+++ b/it_request_forms/013_membership_support_form--it_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>membership_prophetประก</t>
+          <t>membership prophetประก</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>membership_prophetประก</t>
+          <t>membership_prophet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>membership_prophetประก</t>
+          <t>membership prophet</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>membership_support_request_details_3_choices</t>
+          <t>membership_prophet_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>membership_prophet</t>
+          <t>membership_prophet_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>membership_prophet</t>
+          <t>membership prophet 1</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>membership_prophet_1</t>
+          <t>membership_prophet_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>membership_prophet_1</t>
+          <t>membership prophet 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>membership_prophet_choices</t>
+          <t>membership_prophet_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>membership_prophet_2</t>
+          <t>membership_prophet_2_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>membership_prophet_2</t>
+          <t>membership prophet 2 1</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1216,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>membership_prophet_2_1</t>
+          <t>membership_prophet_2_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>membership_prophet_2_1</t>
+          <t>membership prophet 2 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>membership_prophet_2_choices</t>
+          <t>membership_prophet_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>membership_prophet_2_2</t>
+          <t>membership_prophet_4_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>membership_prophet_2_2</t>
+          <t>membership prophet 4 1</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>membership_prophet_4_1</t>
+          <t>membership_prophet_4_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>membership_prophet_4_1</t>
+          <t>membership prophet 4 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>membership_prophet_4_choices</t>
+          <t>membership_prophet_6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>membership_prophet_4_2</t>
+          <t>membership_prophet_6_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>membership_prophet_4_2</t>
+          <t>membership prophet 6 1</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>membership_prophet_6_1</t>
+          <t>membership_prophet_6_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>membership_prophet_6_1</t>
+          <t>membership prophet 6 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>membership_prophet_6_choices</t>
+          <t>membership_prophet_8_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>membership_prophet_6_2</t>
+          <t>membership_prophet_8_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>membership_prophet_6_2</t>
+          <t>membership prophet 8 1</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>membership_prophet_8_1</t>
+          <t>membership_prophet_8_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>membership_prophet_8_1</t>
+          <t>membership prophet 8 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>membership_prophet_8_choices</t>
+          <t>membership_prophet_11_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>membership_prophet_8_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>membership_prophet_8_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>membership_prophet_11_choices</t>
+          <t>membership_pro_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>membership_pro_choices</t>
+          <t>membership_prophet_18_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>membership_prophet_18_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>membership prophet 18 1</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>membership_prophet_18_1</t>
+          <t>membership_prophet_18_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>membership_prophet_18_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>membership_prophet_18_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>membership_prophet_18_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>membership_prophet_18_2</t>
+          <t>membership prophet 18 2</t>
         </is>
       </c>
     </row>
